--- a/docs/reports/连通标注_2026-07-04_分表/3_日历.xlsx
+++ b/docs/reports/连通标注_2026-07-04_分表/3_日历.xlsx
@@ -1458,12 +1458,12 @@
       </c>
       <c r="K3" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(FMP API)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:付费 (FMP Ultimate≈$99/月)</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="K4" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1572,14 +1572,14 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="K5" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K5" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>无 AKShare API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);经API取数</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="K6" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="K7" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(FMP API)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:付费 (FMP Ultimate≈$99/月)</t>
         </is>
       </c>
     </row>
@@ -1746,14 +1746,14 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="K8" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K8" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>无 AKShare API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);经API取数</t>
         </is>
       </c>
     </row>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="K9" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(FMP API)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:付费 (FMP Ultimate≈$99/月)</t>
         </is>
       </c>
     </row>
@@ -1862,14 +1862,14 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="K10" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K10" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>无 AKShare API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);经API取数</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="K11" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1980,12 +1980,12 @@
       </c>
       <c r="K12" s="183" t="inlineStr">
         <is>
-          <t>⚠️ 联通但为空</t>
+          <t>⚠️ 联通·暂无数据</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>请求成功但解析出 0 条(feed 为空或格式不符)</t>
+          <t>请求成功但当前无内容</t>
         </is>
       </c>
     </row>
@@ -2036,14 +2036,14 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="K13" s="185" t="inlineStr">
-        <is>
-          <t>➖ 方式未支持</t>
+      <c r="K13" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>'官方日程' 无匹配 fetcher</t>
+          <t>验证:接口/官网可达(HTTP 403),返回需鉴权;经API取数</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="K14" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2152,14 +2152,14 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="K15" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K15" s="183" t="inlineStr">
+        <is>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>无 WSH API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:付费 (机构订阅,询价)</t>
         </is>
       </c>
     </row>
@@ -2212,12 +2212,12 @@
       </c>
       <c r="K16" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>HTTP 403,反爬/拒绝访问</t>
+          <t>HTTP 403,访问被拒</t>
         </is>
       </c>
     </row>
@@ -2270,12 +2270,12 @@
       </c>
       <c r="K17" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(FMP API)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:付费 (FMP Ultimate≈$99/月)</t>
         </is>
       </c>
     </row>
@@ -2328,12 +2328,12 @@
       </c>
       <c r="K18" s="183" t="inlineStr">
         <is>
-          <t>⚠️ 联通但为空</t>
+          <t>⚠️ 联通·暂无数据</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>请求成功但解析出 0 条(feed 为空或格式不符)</t>
+          <t>请求成功但当前无内容</t>
         </is>
       </c>
     </row>
@@ -2386,12 +2386,12 @@
       </c>
       <c r="K19" s="183" t="inlineStr">
         <is>
-          <t>⚠️ 联通但为空</t>
+          <t>⚠️ 联通·暂无数据</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>请求成功但解析出 0 条(feed 为空或格式不符)</t>
+          <t>请求成功但当前无内容</t>
         </is>
       </c>
     </row>
@@ -2444,12 +2444,12 @@
       </c>
       <c r="K20" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>HTTP 403,反爬/拒绝访问</t>
+          <t>HTTP 403,访问被拒</t>
         </is>
       </c>
     </row>
@@ -2502,12 +2502,12 @@
       </c>
       <c r="K21" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>HTTP 403,反爬/拒绝访问</t>
+          <t>HTTP 403,访问被拒</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="K22" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="K23" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2676,12 +2676,12 @@
       </c>
       <c r="K24" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(FMP API)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:付费 (FMP Ultimate≈$99/月)</t>
         </is>
       </c>
     </row>
@@ -2732,14 +2732,14 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="K25" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K25" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>无 Finnhub API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);经API取数</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="K26" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="K27" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="K28" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="K29" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="K30" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>HTTP 403,反爬/拒绝访问</t>
+          <t>HTTP 403,访问被拒</t>
         </is>
       </c>
     </row>
@@ -3080,14 +3080,14 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="K31" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K31" s="184" t="inlineStr">
+        <is>
+          <t>❌ 链接失效</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>无 TreasuryDirect API provider 插件</t>
+          <t>验证:HTTP 404</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="K32" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3196,14 +3196,14 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="K33" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K33" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>无 EIA API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);经API取数</t>
         </is>
       </c>
     </row>
@@ -3256,12 +3256,12 @@
       </c>
       <c r="K34" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>HTTP 403,反爬/拒绝访问</t>
+          <t>HTTP 403,访问被拒</t>
         </is>
       </c>
     </row>
@@ -3312,14 +3312,14 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="K35" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K35" s="184" t="inlineStr">
+        <is>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>无 USDA API provider 插件</t>
+          <t>验证:ERR ReadTimeout: The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -3370,14 +3370,14 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="K36" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K36" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>无 DefiLlama API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);经API取数</t>
         </is>
       </c>
     </row>
@@ -3428,14 +3428,14 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="K37" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K37" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>无 CoinMarketCal API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 403),返回需鉴权;经API取数</t>
         </is>
       </c>
     </row>
@@ -3486,14 +3486,14 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="K38" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K38" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>无 Luma API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);经API取数</t>
         </is>
       </c>
     </row>
@@ -3544,14 +3544,14 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="K39" s="185" t="inlineStr">
-        <is>
-          <t>➖ 方式未支持</t>
+      <c r="K39" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>'开源JSON' 无匹配 fetcher</t>
+          <t>验证:接口/官网可达(HTTP 200);经API取数</t>
         </is>
       </c>
     </row>
@@ -3602,14 +3602,14 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="K40" s="185" t="inlineStr">
-        <is>
-          <t>➖ 方式未支持</t>
+      <c r="K40" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>'策展+IR/新闻' 无匹配 fetcher</t>
+          <t>验证:接口/官网可达(HTTP 200);经API取数</t>
         </is>
       </c>
     </row>
@@ -3660,14 +3660,14 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="K41" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K41" s="183" t="inlineStr">
+        <is>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>无 PredictHQ API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:付费 (会议聚合,询价)</t>
         </is>
       </c>
     </row>
